--- a/data/trans_dic/P19D_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,48; 97,2</t>
+          <t>92,55; 97,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,4; 98,4</t>
+          <t>94,44; 98,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,15; 97,36</t>
+          <t>92,81; 97,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,68; 98,35</t>
+          <t>94,48; 98,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,25; 98,51</t>
+          <t>94,15; 98,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,04; 97,39</t>
+          <t>91,81; 97,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,02; 97,11</t>
+          <t>91,75; 97,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,7</t>
+          <t>96,46; 98,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,2; 97,47</t>
+          <t>94,04; 97,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,17; 97,41</t>
+          <t>94,14; 97,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93,18; 96,7</t>
+          <t>93,52; 96,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,09; 98,25</t>
+          <t>96,09; 98,21</t>
         </is>
       </c>
     </row>
@@ -804,47 +804,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>96,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,14; 97,05</t>
+          <t>90,52; 96,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,83; 94,51</t>
+          <t>88,08; 94,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,49; 95,43</t>
+          <t>89,37; 95,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95,08; 98,16</t>
+          <t>94,79; 98,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,69; 97,97</t>
+          <t>94,02; 98,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,9; 95,93</t>
+          <t>89,96; 96,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,32; 96,85</t>
+          <t>91,74; 97,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,5; 98,47</t>
+          <t>95,69; 98,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93,37; 97,13</t>
+          <t>93,53; 97,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,75; 94,41</t>
+          <t>89,34; 94,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,47; 95,49</t>
+          <t>91,51; 95,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,82; 98,04</t>
+          <t>95,89; 97,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,86; 94,85</t>
+          <t>89,72; 94,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,93; 89,88</t>
+          <t>84,15; 90,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 93,66</t>
+          <t>87,88; 93,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 93,21</t>
+          <t>88,53; 94,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,84; 97,03</t>
+          <t>88,17; 96,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,05; 96,68</t>
+          <t>90,06; 96,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,74; 94,27</t>
+          <t>83,67; 94,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,79; 98,03</t>
+          <t>92,9; 97,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,61; 94,82</t>
+          <t>90,67; 94,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,87; 91,76</t>
+          <t>86,81; 91,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87,48; 92,75</t>
+          <t>87,61; 92,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 94,26</t>
+          <t>90,63; 94,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,9; 93,68</t>
+          <t>89,86; 93,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,9; 83,93</t>
+          <t>78,65; 84,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,34; 93,11</t>
+          <t>89,46; 93,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,67; 93,25</t>
+          <t>88,7; 92,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,51; 95,01</t>
+          <t>90,53; 95,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,79; 92,56</t>
+          <t>87,64; 92,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,6; 92,27</t>
+          <t>87,68; 92,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,3; 98,35</t>
+          <t>94,42; 96,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,86; 93,67</t>
+          <t>90,73; 93,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83,38; 87,09</t>
+          <t>83,41; 86,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,39; 92,41</t>
+          <t>89,4; 92,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,85; 96,02</t>
+          <t>91,57; 93,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,88; 89,3</t>
+          <t>80,5; 89,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,04; 83,34</t>
+          <t>75,01; 82,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,59; 88,29</t>
+          <t>80,76; 87,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,46; 84,79</t>
+          <t>76,78; 84,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,45; 94,52</t>
+          <t>89,49; 94,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,41; 86,51</t>
+          <t>80,85; 86,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,53</t>
+          <t>87,33; 92,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,28; 93,98</t>
+          <t>89,25; 92,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87,36; 91,91</t>
+          <t>87,37; 92,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,58; 84,17</t>
+          <t>79,42; 84,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85,33; 89,78</t>
+          <t>85,45; 89,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,77; 90,41</t>
+          <t>85,21; 88,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,93; 98,69</t>
+          <t>93,88; 98,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,44; 93,97</t>
+          <t>86,04; 94,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,1; 91,09</t>
+          <t>82,14; 91,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,77; 96,65</t>
+          <t>86,04; 97,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,84</t>
+          <t>89,17; 92,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,54; 89,18</t>
+          <t>84,74; 89,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,57; 91,84</t>
+          <t>87,77; 91,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,59; 93,93</t>
+          <t>90,41; 93,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90,45; 93,7</t>
+          <t>90,35; 93,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85,79; 89,62</t>
+          <t>85,9; 89,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87,38; 90,99</t>
+          <t>87,21; 91,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,78; 93,95</t>
+          <t>90,42; 94,04</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>91,58; 93,7</t>
+          <t>91,68; 93,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84,95; 87,51</t>
+          <t>84,82; 87,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,37; 91,66</t>
+          <t>89,5; 91,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65,43; 92,16</t>
+          <t>90,41; 92,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,01; 93,94</t>
+          <t>92,0; 93,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,96; 90,2</t>
+          <t>87,89; 90,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,03; 92,21</t>
+          <t>89,99; 92,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94,01; 95,86</t>
+          <t>93,66; 94,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>92,15; 93,58</t>
+          <t>92,13; 93,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86,88; 88,69</t>
+          <t>86,83; 88,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,11; 91,68</t>
+          <t>90,13; 91,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,18; 93,75</t>
+          <t>92,32; 93,57</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486324</t>
+          <t>527447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>433018</t>
+          <t>472577</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>919344</t>
+          <t>1000024</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>358660; 376929</t>
+          <t>358903; 377280</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>371235; 386936</t>
+          <t>371383; 387230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>360198; 376481</t>
+          <t>358894; 376208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>473955; 492346</t>
+          <t>513576; 534203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>252868; 264297</t>
+          <t>252592; 264321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>268759; 284396</t>
+          <t>268099; 283999</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>290607; 306684</t>
+          <t>289766; 306581</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>427275; 437129</t>
+          <t>466287; 476765</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>618072; 639509</t>
+          <t>617014; 639621</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>645275; 667482</t>
+          <t>645111; 667268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>654611; 679347</t>
+          <t>657015; 679899</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>906540; 926981</t>
+          <t>986845; 1008520</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435687</t>
+          <t>464467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>367802</t>
+          <t>405799</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>803489</t>
+          <t>870266</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>273619; 291338</t>
+          <t>271760; 290590</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>336105; 361693</t>
+          <t>337083; 362257</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>282432; 301194</t>
+          <t>282062; 301556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>427100; 440960</t>
+          <t>455130; 470742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>312515; 326801</t>
+          <t>313606; 327585</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>281835; 300733</t>
+          <t>282022; 301260</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>304606; 323082</t>
+          <t>306018; 323590</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>361109; 372314</t>
+          <t>399192; 410491</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>591761; 615575</t>
+          <t>592770; 615310</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>624849; 657273</t>
+          <t>621950; 656909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>593841; 619884</t>
+          <t>594056; 619896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>792713; 811136</t>
+          <t>860452; 879270</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384986</t>
+          <t>427399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>159728</t>
+          <t>178669</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>544714</t>
+          <t>606067</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>386658; 408108</t>
+          <t>386020; 407220</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>448632; 480460</t>
+          <t>449846; 482490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>354832; 379524</t>
+          <t>356088; 378786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154618; 616799</t>
+          <t>411476; 438751</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>124440; 135906</t>
+          <t>123498; 135823</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>216805; 232777</t>
+          <t>216819; 232250</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>116747; 131429</t>
+          <t>116650; 131246</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154172; 162880</t>
+          <t>172921; 182185</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>516798; 540807</t>
+          <t>517141; 540616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>673482; 711426</t>
+          <t>673035; 709464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>476441; 505174</t>
+          <t>477172; 505637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>248859; 780380</t>
+          <t>589946; 617653</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916318</t>
+          <t>995708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>927150</t>
+          <t>798980</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1843468</t>
+          <t>1794688</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>784180; 817147</t>
+          <t>783824; 816233</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>765036; 813811</t>
+          <t>762631; 814636</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>785769; 818895</t>
+          <t>786779; 821696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>896444; 932195</t>
+          <t>972232; 1013142</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>539650; 566502</t>
+          <t>539780; 566577</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>610861; 644042</t>
+          <t>609812; 644516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>599234; 631166</t>
+          <t>599750; 631085</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>913633; 942901</t>
+          <t>788798; 808394</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1334357; 1375527</t>
+          <t>1332336; 1373727</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1388786; 1450514</t>
+          <t>1389166; 1448332</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1397687; 1444920</t>
+          <t>1397748; 1443850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1818430; 1880400</t>
+          <t>1768669; 1815429</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>412338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>749595</t>
+          <t>725103</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1104663</t>
+          <t>1137442</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>198046; 221404</t>
+          <t>199590; 221911</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>301936; 335332</t>
+          <t>301816; 333711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>342635; 375365</t>
+          <t>343380; 373217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>334253; 370674</t>
+          <t>390134; 429970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>407959; 431096</t>
+          <t>408151; 431502</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>540107; 581086</t>
+          <t>543109; 581494</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>487506; 515830</t>
+          <t>486875; 515864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>728849; 767182</t>
+          <t>710898; 738646</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>614990; 647018</t>
+          <t>615095; 648204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>854759; 904002</t>
+          <t>853035; 903140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838458; 882266</t>
+          <t>839642; 881474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1075214; 1133309</t>
+          <t>1111676; 1158971</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211413</t>
+          <t>208136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>685948</t>
+          <t>753419</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>897361</t>
+          <t>961554</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>199354; 209461</t>
+          <t>199253; 209448</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189807; 208743</t>
+          <t>191132; 208872</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>198318; 220016</t>
+          <t>198405; 220518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>187948; 222156</t>
+          <t>191491; 217029</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>841582; 877865</t>
+          <t>843206; 878120</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>782456; 825439</t>
+          <t>784317; 826645</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>721624; 756738</t>
+          <t>723236; 757930</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>672261; 696990</t>
+          <t>738179; 766132</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1047314; 1084865</t>
+          <t>1046097; 1083653</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>984667; 1028590</t>
+          <t>985934; 1030498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>931123; 969571</t>
+          <t>929312; 969945</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>872537; 913092</t>
+          <t>939454; 977048</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2789798</t>
+          <t>3035494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3323240</t>
+          <t>3334547</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6113037</t>
+          <t>6370041</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2244386; 2296292</t>
+          <t>2246811; 2296952</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2467545; 2541819</t>
+          <t>2463870; 2544753</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2371691; 2432385</t>
+          <t>2375017; 2436186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2144826; 3021333</t>
+          <t>2997441; 3068316</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2520975; 2573703</t>
+          <t>2520572; 2574483</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2761545; 2831755</t>
+          <t>2759201; 2830999</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2569837; 2631848</t>
+          <t>2568753; 2629667</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3294230; 3359138</t>
+          <t>3310873; 3356635</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4783131; 4857255</t>
+          <t>4782318; 4853960</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5251062; 5360282</t>
+          <t>5248164; 5355595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4963306; 5049732</t>
+          <t>4964611; 5048938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5302580; 6358853</t>
+          <t>6324168; 6409938</t>
         </is>
       </c>
     </row>
